--- a/data/trans_dic/P19F$noche-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,43; 83,79</t>
+          <t>75,27; 84,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,12; 91,64</t>
+          <t>85,06; 91,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,85; 86,96</t>
+          <t>81,64; 86,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,55; 81,65</t>
+          <t>74,73; 81,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,51; 84,52</t>
+          <t>77,53; 84,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,24; 82,12</t>
+          <t>77,24; 81,99</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>61,72; 71,37</t>
+          <t>62,16; 71,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,26; 71,68</t>
+          <t>62,25; 71,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,43; 70,23</t>
+          <t>62,96; 70,19</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,08; 87,8</t>
+          <t>81,23; 87,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,28; 88,38</t>
+          <t>81,1; 88,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,31; 87,24</t>
+          <t>82,29; 87,4</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,56; 79,59</t>
+          <t>75,69; 79,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,87; 82,56</t>
+          <t>78,57; 82,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,76; 80,66</t>
+          <t>77,73; 80,68</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>273605; 303923</t>
+          <t>273020; 305324</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>320170; 344705</t>
+          <t>319944; 344538</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>604755; 642538</t>
+          <t>603226; 642614</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>419875; 459858</t>
+          <t>420873; 460984</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>418989; 456928</t>
+          <t>419138; 455673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>852571; 906453</t>
+          <t>852567; 905002</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>248604; 287484</t>
+          <t>250372; 289976</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>238912; 275095</t>
+          <t>238904; 275910</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498889; 552372</t>
+          <t>495185; 552088</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>364941; 395148</t>
+          <t>365587; 395365</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>359278; 390664</t>
+          <t>358475; 390565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>734289; 778262</t>
+          <t>734163; 779731</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1344079; 1415670</t>
+          <t>1346408; 1417911</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1374368; 1438597</t>
+          <t>1369135; 1436644</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2738106; 2840362</t>
+          <t>2737006; 2840885</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$noche-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Habitat-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,27; 84,17</t>
+          <t>75,58; 84,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85,06; 91,6</t>
+          <t>85,12; 91,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,64; 86,97</t>
+          <t>81,93; 87,3</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>74,73; 81,85</t>
+          <t>74,52; 81,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,53; 84,29</t>
+          <t>77,34; 84,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,24; 81,99</t>
+          <t>77,26; 82,17</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62,16; 71,99</t>
+          <t>61,82; 71,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62,25; 71,9</t>
+          <t>62,46; 71,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,96; 70,19</t>
+          <t>63,21; 70,17</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,23; 87,84</t>
+          <t>81,25; 87,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,1; 88,35</t>
+          <t>81,14; 88,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,29; 87,4</t>
+          <t>82,27; 87,2</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,69; 79,71</t>
+          <t>75,62; 79,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,57; 82,45</t>
+          <t>78,66; 82,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,73; 80,68</t>
+          <t>77,77; 80,66</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>273020; 305324</t>
+          <t>274161; 304738</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>319944; 344538</t>
+          <t>320168; 344867</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>603226; 642614</t>
+          <t>605360; 645031</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>420873; 460984</t>
+          <t>419687; 461530</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>419138; 455673</t>
+          <t>418093; 456480</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>852567; 905002</t>
+          <t>852775; 907022</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>250372; 289976</t>
+          <t>249012; 288553</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>238904; 275910</t>
+          <t>239695; 275679</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>495185; 552088</t>
+          <t>497157; 551957</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>365587; 395365</t>
+          <t>365670; 395958</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>358475; 390565</t>
+          <t>358674; 392269</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>734163; 779731</t>
+          <t>733925; 777886</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1346408; 1417911</t>
+          <t>1345093; 1415764</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1369135; 1436644</t>
+          <t>1370750; 1440189</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2737006; 2840885</t>
+          <t>2738440; 2840308</t>
         </is>
       </c>
     </row>
